--- a/output/stock_quant_scores/RACE_info.xlsx
+++ b/output/stock_quant_scores/RACE_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FT2"/>
+  <dimension ref="A1:FX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,235 +1071,255 @@
       </c>
       <c r="DZ1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1384,7 +1404,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. John Jacob Philip Elkann', 'age': 48, 'title': 'Executive Chairman', 'yearBorn': 1976, 'fiscalYear': 2024, 'totalPay': 1848628, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Benedetto  Vigna', 'age': 55, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 5734244, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Antonio Picca Piccon', 'age': 60, 'title': 'Chief Financial Officer', 'yearBorn': 1964, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Nicoletta  Russo', 'title': 'Head of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Carlo  Daneo', 'age': 56, 'title': 'General Counsel', 'yearBorn': 1968, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Marco  Lovati', 'age': 52, 'title': 'Chief Internal Audit, Risk and Compliance Officer', 'yearBorn': 1972, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Enrico  Galliera', 'age': 58, 'title': 'Chief Marketing &amp; Commercial Officer', 'yearBorn': 1966, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michele  Antoniazzi', 'age': 55, 'title': 'Chief Human Resources Officer', 'yearBorn': 1969, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Flavio  Manzoni', 'age': 59, 'title': 'Chief Design Officer', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Davide  Abate', 'age': 40, 'title': 'Chief Industrial Officer', 'yearBorn': 1984, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. John Jacob Philip Elkann', 'age': 48, 'title': 'Executive Chairman', 'yearBorn': 1976, 'fiscalYear': 2024, 'totalPay': 1832429, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Benedetto  Vigna', 'age': 55, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 5683997, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Antonio Picca Piccon', 'age': 60, 'title': 'Chief Financial Officer', 'yearBorn': 1964, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Nicoletta  Russo', 'title': 'Head of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Carlo  Daneo', 'age': 56, 'title': 'General Counsel', 'yearBorn': 1968, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Marco  Lovati', 'age': 52, 'title': 'Chief Internal Audit, Risk and Compliance Officer', 'yearBorn': 1972, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Enrico  Galliera', 'age': 58, 'title': 'Chief Marketing &amp; Commercial Officer', 'yearBorn': 1966, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michele  Antoniazzi', 'age': 55, 'title': 'Chief Human Resources Officer', 'yearBorn': 1969, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Flavio  Manzoni', 'age': 59, 'title': 'Chief Design Officer', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Davide  Abate', 'age': 40, 'title': 'Chief Industrial Officer', 'yearBorn': 1984, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1420,34 +1440,34 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>486.5</v>
+        <v>473.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>479.53</v>
+        <v>474.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>477.94</v>
+        <v>472.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>481.525</v>
+        <v>476.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>486.5</v>
+        <v>473.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>479.53</v>
+        <v>474.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>477.94</v>
+        <v>472.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>481.525</v>
+        <v>476.07</v>
       </c>
       <c r="AJ2" t="n">
         <v>3.38</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AL2" t="n">
         <v>1745366400</v>
@@ -1462,40 +1482,40 @@
         <v>0.699</v>
       </c>
       <c r="AP2" t="n">
-        <v>45.761475</v>
+        <v>45.445503</v>
       </c>
       <c r="AQ2" t="n">
-        <v>50.22718</v>
+        <v>49.88038</v>
       </c>
       <c r="AR2" t="n">
-        <v>187411</v>
+        <v>183399</v>
       </c>
       <c r="AS2" t="n">
-        <v>187429</v>
+        <v>172203</v>
       </c>
       <c r="AT2" t="n">
-        <v>407317</v>
+        <v>400334</v>
       </c>
       <c r="AU2" t="n">
-        <v>319490</v>
+        <v>336680</v>
       </c>
       <c r="AV2" t="n">
-        <v>319490</v>
+        <v>336680</v>
       </c>
       <c r="AW2" t="n">
-        <v>477.91</v>
+        <v>468</v>
       </c>
       <c r="AX2" t="n">
-        <v>478.26</v>
+        <v>488.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>85184126976</v>
+        <v>84595957760</v>
       </c>
       <c r="BB2" t="n">
         <v>391.54</v>
@@ -1510,19 +1530,19 @@
         <v>31.66</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.242119</v>
+        <v>12.157591</v>
       </c>
       <c r="BG2" t="n">
-        <v>477.069</v>
+        <v>475.6796</v>
       </c>
       <c r="BH2" t="n">
-        <v>461.89896</v>
+        <v>462.29614</v>
       </c>
       <c r="BI2" t="n">
         <v>2.986</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0061377184</v>
+        <v>0.0063106283</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -1533,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>88396791808</v>
+        <v>86411444224</v>
       </c>
       <c r="BN2" t="n">
         <v>0.22912</v>
@@ -1545,40 +1565,40 @@
         <v>177961888</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2593698</v>
+        <v>2521813</v>
       </c>
       <c r="BR2" t="n">
-        <v>2121797</v>
+        <v>2585504</v>
       </c>
       <c r="BS2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BT2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0146</v>
+        <v>0.014199999</v>
       </c>
       <c r="BV2" t="n">
         <v>0.30507</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.41764</v>
+        <v>0.41766</v>
       </c>
       <c r="BX2" t="n">
-        <v>4.76</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>50.7414</v>
+        <v>49.3351</v>
       </c>
       <c r="BZ2" t="n">
-        <v>179017535</v>
+        <v>180178747</v>
       </c>
       <c r="CA2" t="n">
         <v>19.873</v>
       </c>
       <c r="CB2" t="n">
-        <v>24.086199</v>
+        <v>23.919891</v>
       </c>
       <c r="CC2" t="n">
         <v>1735603200</v>
@@ -1602,16 +1622,16 @@
         <v>9.529999999999999</v>
       </c>
       <c r="CJ2" t="n">
-        <v>12.704</v>
+        <v>12.419</v>
       </c>
       <c r="CK2" t="n">
-        <v>37.983</v>
+        <v>37.13</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.02613318</v>
+        <v>0.011167645</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CN2" t="n">
         <v>3.438</v>
@@ -1625,19 +1645,19 @@
         </is>
       </c>
       <c r="CQ2" t="n">
-        <v>478.665</v>
+        <v>475.36</v>
       </c>
       <c r="CR2" t="n">
-        <v>610.40027</v>
+        <v>608.828</v>
       </c>
       <c r="CS2" t="n">
-        <v>445.56403</v>
+        <v>444.41632</v>
       </c>
       <c r="CT2" t="n">
-        <v>531.8214</v>
+        <v>530.45154</v>
       </c>
       <c r="CU2" t="n">
-        <v>546.6622</v>
+        <v>545.2541</v>
       </c>
       <c r="CV2" t="n">
         <v>1.75</v>
@@ -1734,7 +1754,7 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>Nasdaq Real Time Price</t>
+          <t>Delayed Quote</t>
         </is>
       </c>
       <c r="DX2" t="b">
@@ -1747,172 +1767,184 @@
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EA2" t="n">
-        <v>1758740012</v>
-      </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EB2" t="n">
+        <v>1758930742</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="ED2" t="inlineStr">
         <is>
           <t>NYQ</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>finmb_280003133</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EF2" t="n">
+      <c r="EH2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EH2" t="b">
+      <c r="EJ2" t="b">
         <v>0</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="EK2" t="n">
+        <v>0.46283</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>475.36</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1445434200000</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0.10308414</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>475.85</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.49002075</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>2.18997</v>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>472.22 - 476.07</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="EW2" t="n">
+        <v>400334</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>83.81998</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.21407768</v>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>391.54 - 519.1</t>
+        </is>
+      </c>
+      <c r="FA2" t="n">
+        <v>-43.73999</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>-0.08426121</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1.1167645</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1746489600</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>1753965000</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>1753965000</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1753965000</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1753966800</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>1753966800</v>
+      </c>
+      <c r="FJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FK2" t="n">
         <v>10.46</v>
       </c>
-      <c r="EJ2" t="n">
+      <c r="FL2" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="EK2" t="n">
+      <c r="FM2" t="n">
         <v>8.978020000000001</v>
       </c>
-      <c r="EL2" t="n">
-        <v>53.31521</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1.5960083</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.0033454455</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>16.766052</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.036298096</v>
-      </c>
-      <c r="EQ2" t="n">
+      <c r="FN2" t="n">
+        <v>52.947086</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>-0.3196106</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>-0.0006719031</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>13.063843</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>0.028258603</v>
+      </c>
+      <c r="FS2" t="n">
         <v>15</v>
       </c>
-      <c r="ER2" t="n">
+      <c r="FT2" t="n">
         <v>0</v>
       </c>
-      <c r="ES2" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>1.8 - Buy</t>
         </is>
       </c>
-      <c r="ET2" t="b">
+      <c r="FV2" t="b">
         <v>0</v>
       </c>
-      <c r="EU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1445434200000</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>-7.8349915</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>477.94 - 481.525</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="EZ2" t="n">
-        <v>407317</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>87.125</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>0.22251877</v>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>391.54 - 519.1</t>
-        </is>
-      </c>
-      <c r="FD2" t="n">
-        <v>-40.434967</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-0.077894375</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>2.613318</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>1746489600</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>1753965000</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>1753965000</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>1753965000</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>1753966800</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>1753966800</v>
-      </c>
-      <c r="FM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="FO2" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="FP2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FQ2" t="n">
-        <v>-1.6104813</v>
-      </c>
-      <c r="FR2" t="n">
-        <v>478.665</v>
-      </c>
-      <c r="FS2" t="inlineStr">
+      <c r="FW2" t="inlineStr">
         <is>
           <t>Ferrari</t>
         </is>
       </c>
-      <c r="FT2" t="n">
-        <v>3.5432</v>
+      <c r="FX2" t="n">
+        <v>3.4598</v>
       </c>
     </row>
   </sheetData>
